--- a/server/data/MO-214.xlsx
+++ b/server/data/MO-214.xlsx
@@ -1,40 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eryálef Vieira\Work Folder\Vale\Projeto_historico_OMs_equipamentos\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4BDF7528-D5CE-4A94-A338-C0E3E75CFB2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{4F2B0E53-E138-48E7-A21A-331F75D3563A}"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet r:id="rId1" sheetId="1" name="Sheet1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -473,18 +448,21 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -496,12 +474,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC0C0C0"/>
-        <bgColor rgb="FF000000"/>
+        <fgColor rgb="FFc0c0c0"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -511,55 +488,80 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+  <cellXfs count="14">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -570,10 +572,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -600,116 +602,82 @@
         <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -721,2888 +689,2893 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:tint val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="9500"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot rev="0" lon="0" lat="0"/>
+            </a:camera>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:tint val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67D5CC3D-BA0C-443B-BE65-AD7290168972}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
   <dimension ref="A1:M68"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5546875" customWidth="1"/>
-    <col min="6" max="6" width="44.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="36" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.44140625" customWidth="1"/>
-    <col min="11" max="11" width="15.6640625" customWidth="1"/>
-    <col min="12" max="12" width="18.44140625" customWidth="1"/>
-    <col min="13" max="13" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="10" width="16.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="11" width="17.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="11" width="15.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="12" width="38.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="12" width="44.71928571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="12" width="28.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="12" width="36.005" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="11" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="12" width="19.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="12" width="15.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="12" width="18.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="13" width="9.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="29.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="6">
         <v>202500457852</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="3" t="s">
+      <c r="D2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="4" t="s">
+      <c r="H2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2" s="3" t="s">
+      <c r="K2" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="3">
+      <c r="M2" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="6">
         <v>202405755276</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="7">
         <v>45334</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="7">
         <v>45334</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="D3" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="5">
+      <c r="H3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="7">
         <v>45303</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L3" s="3" t="s">
+      <c r="K3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="M3" s="3">
+      <c r="M3" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="6">
         <v>202405487146</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="D4" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" s="4" t="s">
+      <c r="H4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="K4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L4" s="3" t="s">
+      <c r="K4" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L4" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="M4" s="3">
+      <c r="M4" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="6">
         <v>201904041885</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="7">
         <v>43780</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="7">
         <v>43780</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="3" t="s">
+      <c r="D5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" s="5">
+      <c r="H5" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="7">
         <v>43749</v>
       </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M5" s="3">
+      <c r="J5" s="8"/>
+      <c r="K5" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M5" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="6">
         <v>201603630164</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="D6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I6" s="4" t="s">
+      <c r="H6" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M6" s="3">
+      <c r="J6" s="8"/>
+      <c r="K6" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M6" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="6">
         <v>201903468985</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="D7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I7" s="4" t="s">
+      <c r="H7" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M7" s="3">
+      <c r="J7" s="8"/>
+      <c r="K7" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M7" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="6">
         <v>201901156410</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="3" t="s">
+      <c r="D8" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I8" s="4" t="s">
+      <c r="H8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M8" s="3">
+      <c r="J8" s="8"/>
+      <c r="K8" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M8" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="6">
         <v>202004862287</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="3" t="s">
+      <c r="D9" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I9" s="4" t="s">
+      <c r="H9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M9" s="3">
+      <c r="J9" s="8"/>
+      <c r="K9" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M9" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="6">
         <v>202205066919</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="7">
         <v>44875</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="7">
         <v>44875</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="3" t="s">
+      <c r="D10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I10" s="5">
+      <c r="H10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" s="7">
         <v>44875</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M10" s="3">
+      <c r="J10" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M10" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="6">
         <v>201701332387</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="7">
         <v>43012</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="7">
         <v>43012</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="3" t="s">
+      <c r="D11" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I11" s="5">
+      <c r="H11" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" s="7">
         <v>43043</v>
       </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M11" s="3">
+      <c r="J11" s="8"/>
+      <c r="K11" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M11" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="6">
         <v>202506083086</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="7">
         <v>45758</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="7">
         <v>45788</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="3" t="s">
+      <c r="D12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I12" s="4" t="s">
+      <c r="H12" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="J12" s="3" t="s">
+      <c r="J12" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L12" s="3" t="s">
+      <c r="K12" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L12" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="6">
         <v>202506083481</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="7">
         <v>45758</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="7">
         <v>45788</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="3" t="s">
+      <c r="D13" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I13" s="4" t="s">
+      <c r="H13" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="J13" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="K13" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L13" s="3" t="s">
+      <c r="K13" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L13" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="M13" s="3">
+      <c r="M13" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="6">
         <v>202303613928</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="3" t="s">
+      <c r="D14" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I14" s="4" t="s">
+      <c r="H14" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I14" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="J14" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M14" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="6">
         <v>202402915154</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="7">
         <v>45605</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="7">
         <v>45605</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="3" t="s">
+      <c r="D15" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I15" s="4" t="s">
+      <c r="H15" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L15" s="3" t="s">
+      <c r="J15" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L15" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="M15" s="3">
+      <c r="M15" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="6">
         <v>202305018438</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="3" t="s">
+      <c r="D16" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H16" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I16" s="4" t="s">
+      <c r="H16" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M16" s="3">
+      <c r="J16" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M16" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="6">
         <v>202306081125</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="3" t="s">
+      <c r="D17" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="G17" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I17" s="4" t="s">
+      <c r="H17" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I17" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M17" s="3">
+      <c r="J17" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M17" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="6">
         <v>202401394436</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" s="3" t="s">
+      <c r="D18" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="G18" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I18" s="4" t="s">
+      <c r="H18" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I18" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="J18" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M18" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="6">
         <v>202305263646</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19" s="7">
         <v>45180</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C19" s="7">
         <v>45180</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" s="3" t="s">
+      <c r="D19" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="G19" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I19" s="5">
+      <c r="H19" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I19" s="7">
         <v>45180</v>
       </c>
-      <c r="J19" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M19" s="3">
+      <c r="J19" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M19" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="6">
         <v>202205766427</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" s="3" t="s">
+      <c r="D20" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="G20" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I20" s="4" t="s">
+      <c r="H20" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I20" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="J20" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M20" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="6">
         <v>201503480283</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B21" s="7">
         <v>42289</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C21" s="7">
         <v>42289</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" s="3" t="s">
+      <c r="D21" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="G21" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I21" s="5">
+      <c r="H21" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I21" s="7">
         <v>42289</v>
       </c>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="J21" s="8"/>
+      <c r="K21" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M21" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="6">
         <v>201703644975</v>
       </c>
-      <c r="B22" s="5">
+      <c r="B22" s="7">
         <v>43049</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C22" s="7">
         <v>43049</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" s="3" t="s">
+      <c r="D22" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="F22" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="G22" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I22" s="5">
+      <c r="H22" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I22" s="7">
         <v>43049</v>
       </c>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M22" s="3">
+      <c r="J22" s="8"/>
+      <c r="K22" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M22" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="6">
         <v>201700764267</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23" s="3" t="s">
+      <c r="D23" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="F23" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="G23" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I23" s="4" t="s">
+      <c r="H23" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I23" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M23" s="3">
+      <c r="J23" s="8"/>
+      <c r="K23" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M23" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="6">
         <v>201700752849</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24" s="3" t="s">
+      <c r="D24" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="F24" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="G24" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I24" s="4" t="s">
+      <c r="H24" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I24" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L24" s="3" t="s">
+      <c r="J24" s="8"/>
+      <c r="K24" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L24" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="M24" s="3">
+      <c r="M24" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="6">
         <v>201701124111</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="3" t="s">
+      <c r="D25" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="F25" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="G25" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="H25" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I25" s="4" t="s">
+      <c r="H25" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I25" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M25" s="3">
+      <c r="J25" s="8"/>
+      <c r="K25" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M25" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="6">
         <v>201602439965</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" s="3" t="s">
+      <c r="D26" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="F26" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="G26" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I26" s="4" t="s">
+      <c r="H26" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I26" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M26" s="3">
+      <c r="J26" s="8"/>
+      <c r="K26" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M26" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="6">
         <v>202204789616</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="3" t="s">
+      <c r="D27" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="F27" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="G27" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I27" s="4" t="s">
+      <c r="H27" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I27" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M27" s="3">
+      <c r="J27" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M27" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="6">
         <v>202102750030</v>
       </c>
-      <c r="B28" s="5">
+      <c r="B28" s="7">
         <v>44415</v>
       </c>
-      <c r="C28" s="5">
+      <c r="C28" s="7">
         <v>44415</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E28" s="3" t="s">
+      <c r="D28" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="F28" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="G28" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H28" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I28" s="5">
+      <c r="H28" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I28" s="7">
         <v>44415</v>
       </c>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L28" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M28" s="3">
+      <c r="J28" s="8"/>
+      <c r="K28" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M28" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="6">
         <v>202105532831</v>
       </c>
-      <c r="B29" s="5">
+      <c r="B29" s="7">
         <v>44621</v>
       </c>
-      <c r="C29" s="5">
+      <c r="C29" s="7">
         <v>44621</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" s="3" t="s">
+      <c r="D29" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="F29" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="G29" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H29" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I29" s="4" t="s">
+      <c r="H29" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I29" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M29" s="3">
+      <c r="J29" s="8"/>
+      <c r="K29" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L29" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M29" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="6">
         <v>202003292725</v>
       </c>
-      <c r="B30" s="5">
+      <c r="B30" s="7">
         <v>44052</v>
       </c>
-      <c r="C30" s="5">
+      <c r="C30" s="7">
         <v>44052</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E30" s="3" t="s">
+      <c r="D30" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="F30" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="G30" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="H30" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I30" s="5">
+      <c r="H30" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I30" s="7">
         <v>44021</v>
       </c>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L30" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M30" s="3">
+      <c r="J30" s="8"/>
+      <c r="K30" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L30" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M30" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="6">
         <v>201904430132</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E31" s="3" t="s">
+      <c r="D31" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="F31" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="G31" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="H31" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I31" s="5">
+      <c r="H31" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I31" s="7">
         <v>43781</v>
       </c>
-      <c r="J31" s="3"/>
-      <c r="K31" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L31" s="3" t="s">
+      <c r="J31" s="8"/>
+      <c r="K31" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L31" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="M31" s="3">
+      <c r="M31" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="6">
         <v>201903511102</v>
       </c>
-      <c r="B32" s="5">
+      <c r="B32" s="7">
         <v>43475</v>
       </c>
-      <c r="C32" s="5">
+      <c r="C32" s="7">
         <v>43475</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E32" s="3" t="s">
+      <c r="D32" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F32" s="3" t="s">
+      <c r="F32" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="G32" s="3" t="s">
+      <c r="G32" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I32" s="5">
+      <c r="H32" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I32" s="7">
         <v>43475</v>
       </c>
-      <c r="J32" s="3"/>
-      <c r="K32" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L32" s="3" t="s">
+      <c r="J32" s="8"/>
+      <c r="K32" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L32" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="6">
         <v>202001497246</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E33" s="3" t="s">
+      <c r="D33" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="F33" s="3" t="s">
+      <c r="F33" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="G33" s="3" t="s">
+      <c r="G33" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I33" s="4" t="s">
+      <c r="H33" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I33" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="J33" s="3"/>
-      <c r="K33" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M33" s="3">
+      <c r="J33" s="8"/>
+      <c r="K33" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L33" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M33" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="6">
         <v>202003707288</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E34" s="3" t="s">
+      <c r="D34" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E34" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="F34" s="3" t="s">
+      <c r="F34" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="G34" s="3" t="s">
+      <c r="G34" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="H34" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I34" s="5">
+      <c r="H34" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I34" s="7">
         <v>43871</v>
       </c>
-      <c r="J34" s="3"/>
-      <c r="K34" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M34" s="3">
+      <c r="J34" s="8"/>
+      <c r="K34" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L34" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M34" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="6">
         <v>202101305537</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E35" s="3" t="s">
+      <c r="D35" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="F35" s="3" t="s">
+      <c r="F35" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="G35" s="3" t="s">
+      <c r="G35" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I35" s="5">
+      <c r="H35" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I35" s="7">
         <v>44231</v>
       </c>
-      <c r="J35" s="3"/>
-      <c r="K35" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M35" s="3">
+      <c r="J35" s="8"/>
+      <c r="K35" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L35" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M35" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="6">
         <v>202104675626</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E36" s="3" t="s">
+      <c r="D36" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E36" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="F36" s="3" t="s">
+      <c r="F36" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="G36" s="3" t="s">
+      <c r="G36" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H36" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I36" s="5">
+      <c r="H36" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I36" s="7">
         <v>44511</v>
       </c>
-      <c r="J36" s="3"/>
-      <c r="K36" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L36" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M36" s="3">
+      <c r="J36" s="8"/>
+      <c r="K36" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L36" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M36" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="6">
         <v>202202521063</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="D37" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E37" s="3" t="s">
+      <c r="D37" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="F37" s="3" t="s">
+      <c r="F37" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="G37" s="3" t="s">
+      <c r="G37" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H37" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I37" s="5">
+      <c r="H37" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I37" s="7">
         <v>44900</v>
       </c>
-      <c r="J37" s="3"/>
-      <c r="K37" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L37" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M37" s="3">
+      <c r="J37" s="8"/>
+      <c r="K37" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L37" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M37" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="6">
         <v>202205563567</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="D38" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E38" s="3" t="s">
+      <c r="D38" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E38" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="F38" s="3" t="s">
+      <c r="F38" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="G38" s="3" t="s">
+      <c r="G38" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H38" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I38" s="5">
+      <c r="H38" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I38" s="7">
         <v>44845</v>
       </c>
-      <c r="J38" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L38" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M38" s="3">
+      <c r="J38" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K38" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L38" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M38" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
       <c r="A39" s="6">
         <v>202302081437</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="D39" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E39" s="3" t="s">
+      <c r="D39" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E39" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="F39" s="3" t="s">
+      <c r="F39" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="G39" s="3" t="s">
+      <c r="G39" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H39" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I39" s="5">
+      <c r="H39" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I39" s="7">
         <v>45021</v>
       </c>
-      <c r="J39" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L39" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M39" s="3">
+      <c r="J39" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K39" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L39" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M39" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="6">
         <v>202305139324</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E40" s="3" t="s">
+      <c r="D40" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E40" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="F40" s="3" t="s">
+      <c r="F40" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="G40" s="3" t="s">
+      <c r="G40" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H40" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I40" s="5">
+      <c r="H40" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I40" s="7">
         <v>44968</v>
       </c>
-      <c r="J40" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L40" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M40" s="3">
+      <c r="J40" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K40" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L40" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M40" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
       <c r="A41" s="6">
         <v>202402123821</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E41" s="3" t="s">
+      <c r="D41" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E41" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="F41" s="3" t="s">
+      <c r="F41" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="G41" s="3" t="s">
+      <c r="G41" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I41" s="5">
+      <c r="H41" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I41" s="7">
         <v>45327</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M41" s="3">
+      <c r="J41" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K41" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L41" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M41" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="6">
         <v>202405223278</v>
       </c>
-      <c r="B42" s="5">
+      <c r="B42" s="7">
         <v>45547</v>
       </c>
-      <c r="C42" s="5">
+      <c r="C42" s="7">
         <v>45547</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E42" s="3" t="s">
+      <c r="D42" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E42" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="F42" s="3" t="s">
+      <c r="F42" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="G42" s="3" t="s">
+      <c r="G42" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="H42" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I42" s="4" t="s">
+      <c r="H42" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I42" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="J42" s="3" t="s">
+      <c r="J42" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L42" s="3" t="s">
+      <c r="K42" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L42" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="M42" s="3">
+      <c r="M42" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="6">
         <v>202502127821</v>
       </c>
-      <c r="B43" s="5">
+      <c r="B43" s="7">
         <v>45694</v>
       </c>
-      <c r="C43" s="5">
+      <c r="C43" s="7">
         <v>45694</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E43" s="3" t="s">
+      <c r="D43" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E43" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="F43" s="3" t="s">
+      <c r="F43" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="G43" s="3" t="s">
+      <c r="G43" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I43" s="5">
+      <c r="H43" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I43" s="7">
         <v>45662</v>
       </c>
-      <c r="J43" s="3" t="s">
+      <c r="J43" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L43" s="3" t="s">
+      <c r="K43" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L43" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="M43" s="3">
+      <c r="M43" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="6">
         <v>202505749158</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E44" s="3" t="s">
+      <c r="D44" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E44" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="F44" s="3" t="s">
+      <c r="F44" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="G44" s="3" t="s">
+      <c r="G44" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I44" s="5">
+      <c r="H44" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I44" s="7">
         <v>45668</v>
       </c>
-      <c r="J44" s="3" t="s">
+      <c r="J44" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L44" s="3" t="s">
+      <c r="K44" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L44" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="M44" s="3">
+      <c r="M44" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
       <c r="A45" s="6">
         <v>201600562739</v>
       </c>
-      <c r="B45" s="5">
+      <c r="B45" s="7">
         <v>42553</v>
       </c>
-      <c r="C45" s="5">
+      <c r="C45" s="7">
         <v>42553</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E45" s="3" t="s">
+      <c r="D45" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E45" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="F45" s="3" t="s">
+      <c r="F45" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="G45" s="3" t="s">
+      <c r="G45" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I45" s="4" t="s">
+      <c r="H45" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I45" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="J45" s="3"/>
-      <c r="K45" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="J45" s="8"/>
+      <c r="K45" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L45" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M45" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="6">
         <v>201601837408</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E46" s="3" t="s">
+      <c r="D46" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E46" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="F46" s="3" t="s">
+      <c r="F46" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="G46" s="3" t="s">
+      <c r="G46" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I46" s="4" t="s">
+      <c r="H46" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I46" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="J46" s="3"/>
-      <c r="K46" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M46" s="3">
+      <c r="J46" s="8"/>
+      <c r="K46" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L46" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M46" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
       <c r="A47" s="6">
         <v>201603589201</v>
       </c>
-      <c r="B47" s="5">
+      <c r="B47" s="7">
         <v>42948</v>
       </c>
-      <c r="C47" s="5">
+      <c r="C47" s="7">
         <v>42948</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E47" s="3" t="s">
+      <c r="D47" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E47" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="F47" s="3" t="s">
+      <c r="F47" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="G47" s="3" t="s">
+      <c r="G47" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I47" s="5">
+      <c r="H47" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I47" s="7">
         <v>42655</v>
       </c>
-      <c r="J47" s="3"/>
-      <c r="K47" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M47" s="3">
+      <c r="J47" s="8"/>
+      <c r="K47" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L47" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M47" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
       <c r="A48" s="6">
         <v>201701907117</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C48" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E48" s="3" t="s">
+      <c r="D48" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E48" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="F48" s="3" t="s">
+      <c r="F48" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="G48" s="3" t="s">
+      <c r="G48" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I48" s="4" t="s">
+      <c r="H48" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I48" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="J48" s="3"/>
-      <c r="K48" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M48" s="3">
+      <c r="J48" s="8"/>
+      <c r="K48" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L48" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M48" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
       <c r="A49" s="6">
         <v>201704023116</v>
       </c>
-      <c r="B49" s="5">
+      <c r="B49" s="7">
         <v>43020</v>
       </c>
-      <c r="C49" s="5">
+      <c r="C49" s="7">
         <v>43020</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E49" s="3" t="s">
+      <c r="D49" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E49" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="F49" s="3" t="s">
+      <c r="F49" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="G49" s="3" t="s">
+      <c r="G49" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I49" s="5">
+      <c r="H49" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I49" s="7">
         <v>43050</v>
       </c>
-      <c r="J49" s="3"/>
-      <c r="K49" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M49" s="3">
+      <c r="J49" s="8"/>
+      <c r="K49" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L49" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M49" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
       <c r="A50" s="6">
         <v>201800419711</v>
       </c>
-      <c r="B50" s="5">
+      <c r="B50" s="7">
         <v>43161</v>
       </c>
-      <c r="C50" s="5">
+      <c r="C50" s="7">
         <v>43161</v>
       </c>
-      <c r="D50" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E50" s="3" t="s">
+      <c r="D50" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E50" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="F50" s="3" t="s">
+      <c r="F50" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="G50" s="3" t="s">
+      <c r="G50" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="H50" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I50" s="4" t="s">
+      <c r="H50" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I50" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="J50" s="3"/>
-      <c r="K50" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L50" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M50" s="3">
+      <c r="J50" s="8"/>
+      <c r="K50" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L50" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M50" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
       <c r="A51" s="6">
         <v>201800420005</v>
       </c>
-      <c r="B51" s="5">
+      <c r="B51" s="7">
         <v>43161</v>
       </c>
-      <c r="C51" s="5">
+      <c r="C51" s="7">
         <v>43161</v>
       </c>
-      <c r="D51" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E51" s="3" t="s">
+      <c r="D51" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E51" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="F51" s="3" t="s">
+      <c r="F51" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="G51" s="3" t="s">
+      <c r="G51" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="H51" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I51" s="4" t="s">
+      <c r="H51" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I51" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="J51" s="3"/>
-      <c r="K51" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L51" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M51" s="3">
+      <c r="J51" s="8"/>
+      <c r="K51" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L51" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M51" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="6">
         <v>201800420150</v>
       </c>
-      <c r="B52" s="5">
+      <c r="B52" s="7">
         <v>43161</v>
       </c>
-      <c r="C52" s="5">
+      <c r="C52" s="7">
         <v>43161</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E52" s="3" t="s">
+      <c r="D52" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E52" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="F52" s="3" t="s">
+      <c r="F52" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="G52" s="3" t="s">
+      <c r="G52" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I52" s="4" t="s">
+      <c r="H52" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I52" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="J52" s="3"/>
-      <c r="K52" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M52" s="3">
+      <c r="J52" s="8"/>
+      <c r="K52" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L52" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M52" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
       <c r="A53" s="6">
         <v>201802883022</v>
       </c>
-      <c r="B53" s="5">
+      <c r="B53" s="7">
         <v>43167</v>
       </c>
-      <c r="C53" s="5">
+      <c r="C53" s="7">
         <v>43167</v>
       </c>
-      <c r="D53" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E53" s="3" t="s">
+      <c r="D53" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E53" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="F53" s="3" t="s">
+      <c r="F53" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="G53" s="3" t="s">
+      <c r="G53" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="H53" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I53" s="4" t="s">
+      <c r="H53" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I53" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="J53" s="3"/>
-      <c r="K53" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L53" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M53" s="3">
+      <c r="J53" s="8"/>
+      <c r="K53" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L53" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M53" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
       <c r="A54" s="6">
         <v>201802760796</v>
       </c>
-      <c r="B54" s="5">
+      <c r="B54" s="7">
         <v>43198</v>
       </c>
-      <c r="C54" s="5">
+      <c r="C54" s="7">
         <v>43198</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E54" s="3" t="s">
+      <c r="D54" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E54" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="F54" s="3" t="s">
+      <c r="F54" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="G54" s="3" t="s">
+      <c r="G54" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I54" s="4" t="s">
+      <c r="H54" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I54" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="J54" s="3"/>
-      <c r="K54" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M54" s="3">
+      <c r="J54" s="8"/>
+      <c r="K54" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L54" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M54" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
       <c r="A55" s="6">
         <v>201900230094</v>
       </c>
-      <c r="B55" s="5">
+      <c r="B55" s="7">
         <v>43467</v>
       </c>
-      <c r="C55" s="5">
+      <c r="C55" s="7">
         <v>43467</v>
       </c>
-      <c r="D55" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E55" s="3" t="s">
+      <c r="D55" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E55" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="F55" s="3" t="s">
+      <c r="F55" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="G55" s="3" t="s">
+      <c r="G55" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="H55" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I55" s="4" t="s">
+      <c r="H55" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I55" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="J55" s="3"/>
-      <c r="K55" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L55" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M55" s="3">
+      <c r="J55" s="8"/>
+      <c r="K55" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L55" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M55" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
       <c r="A56" s="6">
         <v>201901510093</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="C56" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="D56" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E56" s="3" t="s">
+      <c r="D56" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E56" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="F56" s="3" t="s">
+      <c r="F56" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="G56" s="3" t="s">
+      <c r="G56" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="H56" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I56" s="4" t="s">
+      <c r="H56" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I56" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="J56" s="3"/>
-      <c r="K56" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L56" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M56" s="3">
+      <c r="J56" s="8"/>
+      <c r="K56" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L56" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M56" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
       <c r="A57" s="6">
         <v>201903547680</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="B57" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="C57" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E57" s="3" t="s">
+      <c r="D57" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E57" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="F57" s="3" t="s">
+      <c r="F57" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="G57" s="3" t="s">
+      <c r="G57" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I57" s="5">
+      <c r="H57" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I57" s="7">
         <v>43565</v>
       </c>
-      <c r="J57" s="3"/>
-      <c r="K57" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M57" s="3">
+      <c r="J57" s="8"/>
+      <c r="K57" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L57" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M57" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
       <c r="A58" s="6">
         <v>202200830188</v>
       </c>
-      <c r="B58" s="5">
+      <c r="B58" s="7">
         <v>44867</v>
       </c>
-      <c r="C58" s="5">
+      <c r="C58" s="7">
         <v>44867</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E58" s="3" t="s">
+      <c r="D58" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E58" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F58" s="3" t="s">
+      <c r="F58" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="G58" s="3" t="s">
+      <c r="G58" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I58" s="4" t="s">
+      <c r="H58" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I58" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="J58" s="3"/>
-      <c r="K58" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M58" s="3">
+      <c r="J58" s="8"/>
+      <c r="K58" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L58" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M58" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
       <c r="A59" s="6">
         <v>202303534550</v>
       </c>
-      <c r="B59" s="5">
+      <c r="B59" s="7">
         <v>45783</v>
       </c>
-      <c r="C59" s="5">
+      <c r="C59" s="7">
         <v>45783</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E59" s="3" t="s">
+      <c r="D59" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E59" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F59" s="3" t="s">
+      <c r="F59" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="G59" s="3" t="s">
+      <c r="G59" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I59" s="4" t="s">
+      <c r="H59" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I59" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L59" s="3" t="s">
+      <c r="J59" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K59" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L59" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
       <c r="A60" s="6">
         <v>201502265050</v>
       </c>
-      <c r="B60" s="5">
+      <c r="B60" s="7">
         <v>42346</v>
       </c>
-      <c r="C60" s="5">
+      <c r="C60" s="7">
         <v>42346</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E60" s="3" t="s">
+      <c r="D60" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E60" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F60" s="3" t="s">
+      <c r="F60" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="G60" s="3" t="s">
+      <c r="G60" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I60" s="5">
+      <c r="H60" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I60" s="7">
         <v>42346</v>
       </c>
-      <c r="J60" s="3"/>
-      <c r="K60" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M60" s="3">
+      <c r="J60" s="8"/>
+      <c r="K60" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L60" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M60" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="6">
         <v>201904415710</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B61" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="C61" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="D61" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E61" s="3" t="s">
+      <c r="D61" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E61" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F61" s="3" t="s">
+      <c r="F61" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="G61" s="3" t="s">
+      <c r="G61" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="H61" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I61" s="5">
+      <c r="H61" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I61" s="7">
         <v>43750</v>
       </c>
-      <c r="J61" s="3"/>
-      <c r="K61" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L61" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M61" s="3">
+      <c r="J61" s="8"/>
+      <c r="K61" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L61" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M61" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="6">
         <v>202405702536</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="B62" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="C62" s="4" t="s">
+      <c r="C62" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E62" s="3" t="s">
+      <c r="D62" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E62" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F62" s="3" t="s">
+      <c r="F62" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="G62" s="3" t="s">
+      <c r="G62" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I62" s="4" t="s">
+      <c r="H62" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I62" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="J62" s="3" t="s">
+      <c r="J62" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L62" s="3" t="s">
+      <c r="K62" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L62" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="9">
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="6">
         <v>202305020781</v>
       </c>
-      <c r="B63" s="4" t="s">
+      <c r="B63" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="C63" s="5">
+      <c r="C63" s="7">
         <v>44968</v>
       </c>
-      <c r="D63" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E63" s="3" t="s">
+      <c r="D63" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E63" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F63" s="3" t="s">
+      <c r="F63" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="G63" s="3" t="s">
+      <c r="G63" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H63" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I63" s="4" t="s">
+      <c r="H63" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I63" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="J63" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K63" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L63" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M63" s="3">
+      <c r="J63" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K63" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L63" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M63" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="6">
         <v>202302149362</v>
       </c>
-      <c r="B64" s="5">
+      <c r="B64" s="7">
         <v>45143</v>
       </c>
-      <c r="C64" s="5">
+      <c r="C64" s="7">
         <v>45143</v>
       </c>
-      <c r="D64" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E64" s="3" t="s">
+      <c r="D64" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E64" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F64" s="3" t="s">
+      <c r="F64" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="G64" s="3" t="s">
+      <c r="G64" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H64" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I64" s="5">
+      <c r="H64" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I64" s="7">
         <v>45143</v>
       </c>
-      <c r="J64" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K64" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L64" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M64" s="3">
+      <c r="J64" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K64" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L64" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M64" s="9">
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
       <c r="A65" s="6">
         <v>202303810370</v>
       </c>
-      <c r="B65" s="5">
+      <c r="B65" s="7">
         <v>45238</v>
       </c>
-      <c r="C65" s="5">
+      <c r="C65" s="7">
         <v>45238</v>
       </c>
-      <c r="D65" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E65" s="3" t="s">
+      <c r="D65" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E65" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F65" s="3" t="s">
+      <c r="F65" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="G65" s="3" t="s">
+      <c r="G65" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H65" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I65" s="5">
+      <c r="H65" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I65" s="7">
         <v>45238</v>
       </c>
-      <c r="J65" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K65" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L65" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M65" s="3">
+      <c r="J65" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K65" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L65" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M65" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="6">
         <v>202100055127</v>
       </c>
-      <c r="B66" s="5">
+      <c r="B66" s="7">
         <v>44317</v>
       </c>
-      <c r="C66" s="5">
+      <c r="C66" s="7">
         <v>44348</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E66" s="3" t="s">
+      <c r="D66" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E66" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="F66" s="3" t="s">
+      <c r="F66" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="G66" s="3" t="s">
+      <c r="G66" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I66" s="5">
+      <c r="H66" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I66" s="7">
         <v>44317</v>
       </c>
-      <c r="J66" s="3"/>
-      <c r="K66" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M66" s="3">
+      <c r="J66" s="8"/>
+      <c r="K66" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L66" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M66" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
       <c r="A67" s="6">
         <v>202200915542</v>
       </c>
-      <c r="B67" s="5">
+      <c r="B67" s="7">
         <v>44867</v>
       </c>
-      <c r="C67" s="5">
+      <c r="C67" s="7">
         <v>44867</v>
       </c>
-      <c r="D67" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E67" s="3" t="s">
+      <c r="D67" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F67" s="3" t="s">
+      <c r="F67" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="G67" s="3" t="s">
+      <c r="G67" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H67" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I67" s="4" t="s">
+      <c r="H67" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I67" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="J67" s="3"/>
-      <c r="K67" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L67" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M67" s="3">
+      <c r="J67" s="8"/>
+      <c r="K67" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L67" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M67" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="6">
         <v>201703295680</v>
       </c>
-      <c r="B68" s="4" t="s">
+      <c r="B68" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="C68" s="4" t="s">
+      <c r="C68" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="D68" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E68" s="3" t="s">
+      <c r="D68" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E68" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F68" s="3" t="s">
+      <c r="F68" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="G68" s="3" t="s">
+      <c r="G68" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="H68" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I68" s="4" t="s">
+      <c r="H68" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I68" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="J68" s="3"/>
-      <c r="K68" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L68" s="3" t="s">
+      <c r="J68" s="8"/>
+      <c r="K68" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L68" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="M68" s="3">
+      <c r="M68" s="9">
         <v>1</v>
       </c>
     </row>
